--- a/tests/eindhoven-500/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_concproduct_Auto_OV_Fiets.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_concproduct_Auto_OV_Fiets.xlsx
@@ -6590,7 +6590,7 @@
         <v>366</v>
       </c>
       <c r="B367">
-        <v>26.70844770933176</v>
+        <v>26.70844770933175</v>
       </c>
       <c r="C367">
         <v>25.58914491483362</v>
@@ -6624,7 +6624,7 @@
         <v>368</v>
       </c>
       <c r="B369">
-        <v>7.630985059809073</v>
+        <v>7.630985059809072</v>
       </c>
       <c r="C369">
         <v>6.889385169378284</v>
@@ -7508,7 +7508,7 @@
         <v>420</v>
       </c>
       <c r="B421">
-        <v>98.12198124820975</v>
+        <v>98.12198124820976</v>
       </c>
       <c r="C421">
         <v>99.18990374683537</v>
